--- a/Configuration Library/ACC_1.5MW_GASENGINE_CDU/equipment/CHW_PUMP_2/CHW_PUMP_2.xlsx
+++ b/Configuration Library/ACC_1.5MW_GASENGINE_CDU/equipment/CHW_PUMP_2/CHW_PUMP_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ariel\Desktop\Configuration Library\ACC_1.5MW_GASENGINE_CDU\equipment\CHW_PUMP_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ArielLuoProjectspue-solver\Configuration Library\ACC_1.5MW_GASENGINE_CDU\equipment\CHW_PUMP_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{187F714E-ABC8-4448-81F8-246B8AAE3B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CD33F38-F780-4762-961A-AA5119FA1620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t>Parameter</t>
   </si>
@@ -96,22 +96,22 @@
     <t>ChatGPT</t>
   </si>
   <si>
+    <t>Operating_Mode</t>
+  </si>
+  <si>
+    <t>power_kW</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Failure</t>
+  </si>
+  <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>Pending vendor data</t>
-  </si>
-  <si>
-    <t>Operating_Mode</t>
-  </si>
-  <si>
-    <t>power_kW</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Failure</t>
+    <t>Engineering curve placeholder; pending vendor data</t>
   </si>
   <si>
     <t>load_ratio</t>
@@ -129,36 +129,66 @@
     <t>Not stored in Equipment Package</t>
   </si>
   <si>
-    <t>Future Update</t>
-  </si>
-  <si>
-    <t>Replace scenario values with vendor curves</t>
+    <t>Curve Method</t>
+  </si>
+  <si>
+    <t>Engineering placeholder: VFD CHW pump cubic affinity curve with minimum power allowance</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>power_kW = rated_power_kW * (0.25 + 0.75 * load_ratio^3)</t>
+  </si>
+  <si>
+    <t>Normal Rated Power</t>
+  </si>
+  <si>
+    <t>15 kW at load_ratio = 1.0</t>
+  </si>
+  <si>
+    <t>Failure Rated Power</t>
+  </si>
+  <si>
+    <t>20 kW at load_ratio = 1.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -173,15 +203,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -194,7 +232,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -236,72 +274,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -309,55 +289,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -366,13 +306,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -406,24 +346,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -449,7 +378,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -566,7 +495,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -609,14 +538,14 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -627,15 +556,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -643,14 +572,14 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -658,97 +587,101 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" customWidth="1"/>
+    <col min="2" max="2" width="8.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>0.1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>9.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>11.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>0.2</v>
-      </c>
-      <c r="B3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>0.3</v>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>0.4</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>0.5</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>0.6</v>
-      </c>
-      <c r="B7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>0.7</v>
-      </c>
-      <c r="B8">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>0.8</v>
-      </c>
-      <c r="B9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>0.9</v>
-      </c>
-      <c r="B10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -756,110 +689,118 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.36328125" customWidth="1"/>
+    <col min="2" max="2" width="8.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>26</v>
+      <c r="B1" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>0.1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>15.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>0.2</v>
-      </c>
-      <c r="B3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>0.3</v>
-      </c>
-      <c r="B4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>0.4</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>0.5</v>
-      </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>0.6</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>0.7</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>0.8</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>0.9</v>
-      </c>
-      <c r="B10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="70.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -887,7 +828,31 @@
         <v>35</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>